--- a/selenium/reports/E2E_Test_Report.xlsx
+++ b/selenium/reports/E2E_Test_Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="626">
   <si>
     <t>End-to-End Test Automation Execution Report</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Pass Rate</t>
   </si>
   <si>
-    <t>93.0%</t>
+    <t>100.0%</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -91,13 +91,13 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>13032 ms</t>
+    <t>12831 ms</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-06-18T13:02:10.026Z</t>
+    <t>2026-06-18T14:18:08.671Z</t>
   </si>
   <si>
     <t>TC-E2E-02</t>
@@ -109,10 +109,10 @@
     <t>Verify login, dashboard stats, and sign out</t>
   </si>
   <si>
-    <t>2484 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:02:12.519Z</t>
+    <t>2406 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:18:11.084Z</t>
   </si>
   <si>
     <t>TC-E2E-03</t>
@@ -124,10 +124,10 @@
     <t>Register and check workout history logs</t>
   </si>
   <si>
-    <t>24690 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:02:37.209Z</t>
+    <t>24733 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:18:35.818Z</t>
   </si>
   <si>
     <t>TC-E2E-04</t>
@@ -139,10 +139,10 @@
     <t>Check favorites list addition and toggling</t>
   </si>
   <si>
-    <t>24580 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:03:01.789Z</t>
+    <t>24451 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:19:00.270Z</t>
   </si>
   <si>
     <t>TC-E2E-05</t>
@@ -154,10 +154,10 @@
     <t>Access settings and enable biometric credentials login</t>
   </si>
   <si>
-    <t>43963 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:03:45.754Z</t>
+    <t>42415 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:19:42.687Z</t>
   </si>
   <si>
     <t>TC-E2E-06</t>
@@ -169,10 +169,10 @@
     <t>Update weight and height and verify dashboard reflects BMI values</t>
   </si>
   <si>
-    <t>33899 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:04:19.656Z</t>
+    <t>29633 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:20:12.324Z</t>
   </si>
   <si>
     <t>TC-E2E-07</t>
@@ -184,10 +184,10 @@
     <t>Complete a yoga workout and check streak values increment</t>
   </si>
   <si>
-    <t>21036 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:04:40.695Z</t>
+    <t>20450 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:20:32.774Z</t>
   </si>
   <si>
     <t>TC-E2E-08</t>
@@ -199,10 +199,10 @@
     <t>Attempt to change user password in configurations</t>
   </si>
   <si>
-    <t>22182 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:05:02.878Z</t>
+    <t>21630 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:20:54.404Z</t>
   </si>
   <si>
     <t>TC-E2E-09</t>
@@ -214,10 +214,10 @@
     <t>Register and request complete account data deletion</t>
   </si>
   <si>
-    <t>22169 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:05:25.048Z</t>
+    <t>21466 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:21:15.872Z</t>
   </si>
   <si>
     <t>TC-E2E-10</t>
@@ -229,10 +229,10 @@
     <t>Route to support page and create support ticket</t>
   </si>
   <si>
-    <t>23889 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:05:48.941Z</t>
+    <t>21549 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:21:37.424Z</t>
   </si>
   <si>
     <t>TC-FUN-01</t>
@@ -247,7 +247,10 @@
     <t>Verify transition between Login and Signup screens</t>
   </si>
   <si>
-    <t>2026-06-18T13:05:57.628Z</t>
+    <t>2173 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:21:45.682Z</t>
   </si>
   <si>
     <t>TC-FUN-02</t>
@@ -259,10 +262,10 @@
     <t>Check Yoga Tab routing and view list</t>
   </si>
   <si>
-    <t>27366 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:06:30.209Z</t>
+    <t>10065 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:22:00.802Z</t>
   </si>
   <si>
     <t>TC-FUN-03</t>
@@ -271,10 +274,10 @@
     <t>Check Profile Tab routing and workout history button</t>
   </si>
   <si>
-    <t>2045 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:06:32.261Z</t>
+    <t>1159 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:22:01.963Z</t>
   </si>
   <si>
     <t>TC-FUN-04</t>
@@ -283,10 +286,10 @@
     <t>Check Settings Tab routing and list items</t>
   </si>
   <si>
-    <t>2005 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:06:34.273Z</t>
+    <t>1164 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:22:03.128Z</t>
   </si>
   <si>
     <t>TC-FUN-05</t>
@@ -295,10 +298,10 @@
     <t>Check Home Tab routing return from Settings</t>
   </si>
   <si>
-    <t>25455 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:06:59.730Z</t>
+    <t>8853 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:22:11.982Z</t>
   </si>
   <si>
     <t>TC-FUN-06</t>
@@ -310,10 +313,10 @@
     <t>Check Start Yoga Quick Action navigation</t>
   </si>
   <si>
-    <t>27625 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:07:27.357Z</t>
+    <t>10956 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:22:22.938Z</t>
   </si>
   <si>
     <t>TC-FUN-07</t>
@@ -322,10 +325,10 @@
     <t>Check Timer Quick Action navigation</t>
   </si>
   <si>
-    <t>27631 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:07:54.988Z</t>
+    <t>11016 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:22:33.955Z</t>
   </si>
   <si>
     <t>TC-FUN-08</t>
@@ -337,165 +340,10 @@
     <t>Route to Account Settings details screen</t>
   </si>
   <si>
-    <t>29873 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:08:24.865Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-09</t>
-  </si>
-  <si>
-    <t>Route to Biometric Login settings</t>
-  </si>
-  <si>
-    <t>Failed: Timeout of 30000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\HP\yoga_app\selenium\tests\functional\functional.test.js)</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>30016 ms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Timeout of 30000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\HP\yoga_app\selenium\tests\functional\functional.test.js)
-    at listOnTimeout (node:internal/timers:605:17)
-    at process.processTimers (node:internal/timers:541:7)</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:08:54.899Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-10</t>
-  </si>
-  <si>
-    <t>Route to Change Password screen</t>
-  </si>
-  <si>
-    <t>30008 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:09:24.976Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-11</t>
-  </si>
-  <si>
-    <t>Route to Contact Us support page</t>
-  </si>
-  <si>
-    <t>30009 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:09:55.024Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-12</t>
-  </si>
-  <si>
-    <t>Route to Delete Account data request page</t>
-  </si>
-  <si>
-    <t>30013 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:10:25.074Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-13</t>
-  </si>
-  <si>
-    <t>Route to Email Support tickets page</t>
-  </si>
-  <si>
-    <t>30000 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:10:55.110Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-14</t>
-  </si>
-  <si>
-    <t>Route to FAQs list page</t>
-  </si>
-  <si>
-    <t>30002 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:11:25.138Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-15</t>
-  </si>
-  <si>
-    <t>Route to Help center guidelines page</t>
-  </si>
-  <si>
-    <t>30003 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:11:55.172Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-16</t>
-  </si>
-  <si>
-    <t>Route to Hide Personal Information toggle screen</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:12:25.206Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-17</t>
-  </si>
-  <si>
-    <t>Route to Language translation options</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:12:55.241Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-18</t>
-  </si>
-  <si>
-    <t>Route to Notification configuration preferences</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:13:25.294Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-19</t>
-  </si>
-  <si>
-    <t>Route to Privacy policy details document</t>
-  </si>
-  <si>
-    <t>30006 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:13:55.340Z</t>
-  </si>
-  <si>
-    <t>TC-FUN-20</t>
-  </si>
-  <si>
-    <t>Route to Send Feedback form screen</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:14:25.380Z</t>
-  </si>
-  <si>
-    <t>"after all" hook for "TC-FUN-20</t>
-  </si>
-  <si>
-    <t>Functional"</t>
-  </si>
-  <si>
-    <t>30019 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:14:55.424Z</t>
+    <t>13048 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:22:47.008Z</t>
   </si>
   <si>
     <t>TC-VAL-01</t>
@@ -510,10 +358,10 @@
     <t>Trigger empty email and password login validation</t>
   </si>
   <si>
-    <t>2386 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:15:04.126Z</t>
+    <t>2090 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:23:15.575Z</t>
   </si>
   <si>
     <t>TC-VAL-02</t>
@@ -522,10 +370,10 @@
     <t>Trigger missing password login validation</t>
   </si>
   <si>
-    <t>2099 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:15:06.225Z</t>
+    <t>2064 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:23:17.640Z</t>
   </si>
   <si>
     <t>TC-VAL-03</t>
@@ -534,10 +382,10 @@
     <t>Trigger missing email login validation</t>
   </si>
   <si>
-    <t>2106 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:15:08.331Z</t>
+    <t>2569 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:23:20.209Z</t>
   </si>
   <si>
     <t>TC-VAL-04</t>
@@ -546,10 +394,10 @@
     <t>Trigger invalid email format validation on login</t>
   </si>
   <si>
-    <t>5137 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:15:13.471Z</t>
+    <t>5337 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:23:25.546Z</t>
   </si>
   <si>
     <t>TC-VAL-05</t>
@@ -561,10 +409,10 @@
     <t>Trigger empty email and password registration validation</t>
   </si>
   <si>
-    <t>7484 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:15:20.959Z</t>
+    <t>6889 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:23:32.437Z</t>
   </si>
   <si>
     <t>TC-VAL-06</t>
@@ -573,10 +421,10 @@
     <t>Trigger weak password registration validation</t>
   </si>
   <si>
-    <t>4283 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:15:25.243Z</t>
+    <t>4363 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:23:36.801Z</t>
   </si>
   <si>
     <t>TC-VAL-07</t>
@@ -585,10 +433,10 @@
     <t>Trigger registration with invalid email format</t>
   </si>
   <si>
-    <t>7228 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:15:32.472Z</t>
+    <t>7415 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:23:44.218Z</t>
   </si>
   <si>
     <t>TC-VAL-08</t>
@@ -597,33 +445,154 @@
     <t>Verify signup form mismatch password field verification</t>
   </si>
   <si>
-    <t>10397 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:15:42.874Z</t>
-  </si>
-  <si>
-    <t>"after all" hook for "TC-VAL-20</t>
+    <t>10468 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:23:54.689Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-09</t>
   </si>
   <si>
     <t>Health_Details</t>
   </si>
   <si>
+    <t>Trigger empty blood pressure format validation</t>
+  </si>
+  <si>
+    <t>6945 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:16.351Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-10</t>
+  </si>
+  <si>
+    <t>Trigger high blood pressure upper bounds check</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:18.415Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-11</t>
+  </si>
+  <si>
+    <t>Trigger empty blood sugar input validation</t>
+  </si>
+  <si>
+    <t>1829 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:20.245Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-12</t>
+  </si>
+  <si>
+    <t>Trigger negative blood sugar validation</t>
+  </si>
+  <si>
+    <t>7048 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:27.294Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-13</t>
+  </si>
+  <si>
+    <t>Trigger high blood sugar upper bounds check</t>
+  </si>
+  <si>
+    <t>7200 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:34.496Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-14</t>
+  </si>
+  <si>
+    <t>Trigger zero heart rate validation check</t>
+  </si>
+  <si>
+    <t>2065 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:36.562Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-15</t>
+  </si>
+  <si>
+    <t>Trigger negative heart rate validation check</t>
+  </si>
+  <si>
+    <t>2269 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:38.833Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-16</t>
+  </si>
+  <si>
+    <t>Trigger pain level exceeding upper limit check</t>
+  </si>
+  <si>
+    <t>2228 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:41.063Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-17</t>
+  </si>
+  <si>
+    <t>Trigger negative pain level check</t>
+  </si>
+  <si>
+    <t>2436 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:43.500Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-18</t>
+  </si>
+  <si>
+    <t>Trigger negative age validation bounds check</t>
+  </si>
+  <si>
+    <t>2057 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:45.558Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-19</t>
+  </si>
+  <si>
+    <t>Trigger zero weight validation bounds check</t>
+  </si>
+  <si>
+    <t>2015 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:47.573Z</t>
+  </si>
+  <si>
+    <t>TC-VAL-20</t>
+  </si>
+  <si>
     <t>Trigger zero height validation bounds check</t>
   </si>
   <si>
-    <t>Validation"</t>
-  </si>
-  <si>
-    <t>Failed: Timeout of 30000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\HP\yoga_app\selenium\tests\validation\validation.test.js)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Timeout of 30000ms exceeded. For async tests and hooks, ensure "done()" is called; if returning a Promise, ensure it resolves. (C:\Users\HP\yoga_app\selenium\tests\validation\validation.test.js)
-    at listOnTimeout (node:internal/timers:605:17)
-    at process.processTimers (node:internal/timers:541:7)</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:16:46.538Z</t>
+    <t>2117 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:24:49.692Z</t>
   </si>
   <si>
     <t>TC-UI-01</t>
@@ -638,175 +607,178 @@
     <t>Verify presence of self_improvement branding icon</t>
   </si>
   <si>
+    <t>6 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:16.193Z</t>
+  </si>
+  <si>
+    <t>TC-UI-02</t>
+  </si>
+  <si>
+    <t>Login_Header</t>
+  </si>
+  <si>
+    <t>Verify typography and wording of Login main title</t>
+  </si>
+  <si>
+    <t>4 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:16.197Z</t>
+  </si>
+  <si>
+    <t>TC-UI-03</t>
+  </si>
+  <si>
+    <t>Verify Email text input placeholder label</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:16.202Z</t>
+  </si>
+  <si>
+    <t>TC-UI-04</t>
+  </si>
+  <si>
+    <t>Verify Password text input placeholder label</t>
+  </si>
+  <si>
+    <t>5 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:16.207Z</t>
+  </si>
+  <si>
+    <t>TC-UI-05</t>
+  </si>
+  <si>
+    <t>Login_Button</t>
+  </si>
+  <si>
+    <t>Verify presence of primary green Login button</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:16.212Z</t>
+  </si>
+  <si>
+    <t>TC-UI-06</t>
+  </si>
+  <si>
+    <t>Signup_Layout</t>
+  </si>
+  <si>
+    <t>Verify routing to Signup and title text presence</t>
+  </si>
+  <si>
+    <t>2176 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:18.390Z</t>
+  </si>
+  <si>
+    <t>TC-UI-07</t>
+  </si>
+  <si>
+    <t>Verify presence of Sign Up action button</t>
+  </si>
+  <si>
+    <t>2258 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:20.650Z</t>
+  </si>
+  <si>
+    <t>TC-UI-08</t>
+  </si>
+  <si>
+    <t>Signup_Navigation</t>
+  </si>
+  <si>
+    <t>Verify presence of Back to Login redirect button</t>
+  </si>
+  <si>
+    <t>2434 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:23.086Z</t>
+  </si>
+  <si>
+    <t>TC-UI-09</t>
+  </si>
+  <si>
+    <t>Dashboard_Header</t>
+  </si>
+  <si>
+    <t>Verify Yoga Dashboard header text</t>
+  </si>
+  <si>
+    <t>65 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:28.007Z</t>
+  </si>
+  <si>
+    <t>TC-UI-10</t>
+  </si>
+  <si>
+    <t>Dashboard_Widgets</t>
+  </si>
+  <si>
+    <t>Verify Minutes practiced card widget header</t>
+  </si>
+  <si>
+    <t>24 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:28.031Z</t>
+  </si>
+  <si>
+    <t>TC-UI-11</t>
+  </si>
+  <si>
+    <t>Verify Sessions completed card widget header</t>
+  </si>
+  <si>
+    <t>26 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:28.058Z</t>
+  </si>
+  <si>
+    <t>TC-UI-12</t>
+  </si>
+  <si>
+    <t>Verify AI accuracy percentage widget header</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:28.066Z</t>
+  </si>
+  <si>
+    <t>TC-UI-13</t>
+  </si>
+  <si>
+    <t>Verify Consecutive Streak days widget header</t>
+  </si>
+  <si>
+    <t>13 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:28.079Z</t>
+  </si>
+  <si>
+    <t>TC-UI-14</t>
+  </si>
+  <si>
+    <t>Dashboard_Layout</t>
+  </si>
+  <si>
+    <t>Verify Start Yoga quick action visual element presence</t>
+  </si>
+  <si>
     <t>7 ms</t>
   </si>
   <si>
-    <t>2026-06-18T13:16:52.680Z</t>
-  </si>
-  <si>
-    <t>TC-UI-02</t>
-  </si>
-  <si>
-    <t>Login_Header</t>
-  </si>
-  <si>
-    <t>Verify typography and wording of Login main title</t>
-  </si>
-  <si>
-    <t>4 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:16:52.684Z</t>
-  </si>
-  <si>
-    <t>TC-UI-03</t>
-  </si>
-  <si>
-    <t>Verify Email text input placeholder label</t>
-  </si>
-  <si>
-    <t>5 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:16:52.689Z</t>
-  </si>
-  <si>
-    <t>TC-UI-04</t>
-  </si>
-  <si>
-    <t>Verify Password text input placeholder label</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:16:52.694Z</t>
-  </si>
-  <si>
-    <t>TC-UI-05</t>
-  </si>
-  <si>
-    <t>Login_Button</t>
-  </si>
-  <si>
-    <t>Verify presence of primary green Login button</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:16:52.700Z</t>
-  </si>
-  <si>
-    <t>TC-UI-06</t>
-  </si>
-  <si>
-    <t>Signup_Layout</t>
-  </si>
-  <si>
-    <t>Verify routing to Signup and title text presence</t>
-  </si>
-  <si>
-    <t>2149 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:16:54.850Z</t>
-  </si>
-  <si>
-    <t>TC-UI-07</t>
-  </si>
-  <si>
-    <t>Verify presence of Sign Up action button</t>
-  </si>
-  <si>
-    <t>2356 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:16:57.207Z</t>
-  </si>
-  <si>
-    <t>TC-UI-08</t>
-  </si>
-  <si>
-    <t>Signup_Navigation</t>
-  </si>
-  <si>
-    <t>Verify presence of Back to Login redirect button</t>
-  </si>
-  <si>
-    <t>2181 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:16:59.390Z</t>
-  </si>
-  <si>
-    <t>TC-UI-09</t>
-  </si>
-  <si>
-    <t>Dashboard_Header</t>
-  </si>
-  <si>
-    <t>Verify Yoga Dashboard header text</t>
-  </si>
-  <si>
-    <t>31 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:04.218Z</t>
-  </si>
-  <si>
-    <t>TC-UI-10</t>
-  </si>
-  <si>
-    <t>Dashboard_Widgets</t>
-  </si>
-  <si>
-    <t>Verify Minutes practiced card widget header</t>
-  </si>
-  <si>
-    <t>34 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:04.254Z</t>
-  </si>
-  <si>
-    <t>TC-UI-11</t>
-  </si>
-  <si>
-    <t>Verify Sessions completed card widget header</t>
-  </si>
-  <si>
-    <t>23 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:04.277Z</t>
-  </si>
-  <si>
-    <t>TC-UI-12</t>
-  </si>
-  <si>
-    <t>Verify AI accuracy percentage widget header</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:04.282Z</t>
-  </si>
-  <si>
-    <t>TC-UI-13</t>
-  </si>
-  <si>
-    <t>Verify Consecutive Streak days widget header</t>
-  </si>
-  <si>
-    <t>10 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:04.293Z</t>
-  </si>
-  <si>
-    <t>TC-UI-14</t>
-  </si>
-  <si>
-    <t>Dashboard_Layout</t>
-  </si>
-  <si>
-    <t>Verify Start Yoga quick action visual element presence</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:04.301Z</t>
+    <t>2026-06-18T14:25:28.088Z</t>
   </si>
   <si>
     <t>TC-UI-15</t>
@@ -815,7 +787,7 @@
     <t>Verify Timer quick action visual element presence</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:04.308Z</t>
+    <t>2026-06-18T14:25:28.094Z</t>
   </si>
   <si>
     <t>TC-SEC-01</t>
@@ -830,10 +802,10 @@
     <t>Verify no hardcoded credentials or API keys in configuration files</t>
   </si>
   <si>
-    <t>11 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:09.220Z</t>
+    <t>8 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:33.161Z</t>
   </si>
   <si>
     <t>TC-SEC-02</t>
@@ -845,10 +817,10 @@
     <t>Check configuration target URLs use secure protocol configurations</t>
   </si>
   <si>
-    <t>3 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:09.224Z</t>
+    <t>1 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:33.163Z</t>
   </si>
   <si>
     <t>TC-SEC-03</t>
@@ -860,7 +832,10 @@
     <t>Programmatically run npm audit to detect critical security advisories</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.373Z</t>
+    <t>3537 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:36.700Z</t>
   </si>
   <si>
     <t>TC-SEC-04</t>
@@ -872,66 +847,63 @@
     <t>Verify git ignores database cache folders and node_modules</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.702Z</t>
+  </si>
+  <si>
+    <t>TC-SEC-05</t>
+  </si>
+  <si>
+    <t>HTML_Security</t>
+  </si>
+  <si>
+    <t>Check for Content Security Policy meta headers presence in web folder</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:36.703Z</t>
+  </si>
+  <si>
+    <t>TC-UNI-01</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Streak_Calculation</t>
+  </si>
+  <si>
+    <t>Calculate streak for empty histories</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:36.706Z</t>
+  </si>
+  <si>
+    <t>TC-UNI-02</t>
+  </si>
+  <si>
+    <t>Calculate streak for active consecutive days</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:36.707Z</t>
+  </si>
+  <si>
+    <t>TC-UNI-03</t>
+  </si>
+  <si>
+    <t>Calculate streak where newest session is broken</t>
+  </si>
+  <si>
     <t>0 ms</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.375Z</t>
-  </si>
-  <si>
-    <t>TC-SEC-05</t>
-  </si>
-  <si>
-    <t>HTML_Security</t>
-  </si>
-  <si>
-    <t>Check for Content Security Policy meta headers presence in web folder</t>
-  </si>
-  <si>
-    <t>1 ms</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:11.376Z</t>
-  </si>
-  <si>
-    <t>TC-UNI-01</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Streak_Calculation</t>
-  </si>
-  <si>
-    <t>Calculate streak for empty histories</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:11.378Z</t>
-  </si>
-  <si>
-    <t>TC-UNI-02</t>
-  </si>
-  <si>
-    <t>Calculate streak for active consecutive days</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:11.379Z</t>
-  </si>
-  <si>
-    <t>TC-UNI-03</t>
-  </si>
-  <si>
-    <t>Calculate streak where newest session is broken</t>
-  </si>
-  <si>
-    <t>2026-06-18T13:17:11.380Z</t>
-  </si>
-  <si>
     <t>TC-UNI-04</t>
   </si>
   <si>
     <t>Calculate streak with duplicated dates in same day</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.708Z</t>
+  </si>
+  <si>
     <t>TC-UNI-05</t>
   </si>
   <si>
@@ -962,15 +934,15 @@
     <t>Calculate streak with multiple gaps</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.709Z</t>
+  </si>
+  <si>
     <t>TC-UNI-10</t>
   </si>
   <si>
     <t>Calculate streak for extremely long histories</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.381Z</t>
-  </si>
-  <si>
     <t>TC-UNI-11</t>
   </si>
   <si>
@@ -983,6 +955,9 @@
     <t>Calculate streak with non-ISO string parsing</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.710Z</t>
+  </si>
+  <si>
     <t>TC-UNI-13</t>
   </si>
   <si>
@@ -998,15 +973,15 @@
     <t>Correctly average multiple integers</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.711Z</t>
+  </si>
+  <si>
     <t>TC-UNI-15</t>
   </si>
   <si>
     <t>Correctly average when total accuracy is zero</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.382Z</t>
-  </si>
-  <si>
     <t>TC-UNI-16</t>
   </si>
   <si>
@@ -1025,7 +1000,7 @@
     <t>Correctly handle decimal rounding down</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.383Z</t>
+    <t>2026-06-18T14:25:36.712Z</t>
   </si>
   <si>
     <t>TC-UNI-19</t>
@@ -1043,9 +1018,6 @@
     <t>Formats seconds under one minute</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.384Z</t>
-  </si>
-  <si>
     <t>TC-UNI-21</t>
   </si>
   <si>
@@ -1058,6 +1030,9 @@
     <t>Formats seconds exceeding one hour</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.713Z</t>
+  </si>
+  <si>
     <t>TC-UNI-23</t>
   </si>
   <si>
@@ -1070,18 +1045,12 @@
     <t>Formats extremely large duration numbers</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.385Z</t>
-  </si>
-  <si>
     <t>TC-UNI-25</t>
   </si>
   <si>
     <t>Formats single digit seconds</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.386Z</t>
-  </si>
-  <si>
     <t>TC-UNI-26</t>
   </si>
   <si>
@@ -1094,6 +1063,9 @@
     <t>Formats exact 10 minutes</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.714Z</t>
+  </si>
+  <si>
     <t>TC-UNI-28</t>
   </si>
   <si>
@@ -1115,15 +1087,15 @@
     <t>Verify high obesity values</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.387Z</t>
-  </si>
-  <si>
     <t>TC-UNI-31</t>
   </si>
   <si>
     <t>Verify extremely low underweight values</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.715Z</t>
+  </si>
+  <si>
     <t>TC-UNI-32</t>
   </si>
   <si>
@@ -1139,15 +1111,15 @@
     <t>Classify overweight and obese BMI</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.388Z</t>
-  </si>
-  <si>
     <t>TC-UNI-34</t>
   </si>
   <si>
     <t>Classify negative and zero BMI</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.716Z</t>
+  </si>
+  <si>
     <t>TC-UNI-35</t>
   </si>
   <si>
@@ -1157,16 +1129,13 @@
     <t>Classify normal and elevated blood pressures</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.389Z</t>
-  </si>
-  <si>
     <t>TC-UNI-36</t>
   </si>
   <si>
     <t>Classify stage 1 and stage 2 hypertensive levels</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.390Z</t>
+    <t>2026-06-18T14:25:36.717Z</t>
   </si>
   <si>
     <t>TC-UNI-37</t>
@@ -1175,7 +1144,7 @@
     <t>Classify hypertensive crisis and invalid levels</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.391Z</t>
+    <t>2026-06-18T14:25:36.718Z</t>
   </si>
   <si>
     <t>TC-UNI-38</t>
@@ -1187,15 +1156,15 @@
     <t>Verify normal burn at low intensity</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.392Z</t>
-  </si>
-  <si>
     <t>TC-UNI-39</t>
   </si>
   <si>
     <t>Verify normal burn at high intensity</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.719Z</t>
+  </si>
+  <si>
     <t>TC-UNI-40</t>
   </si>
   <si>
@@ -1211,7 +1180,7 @@
     <t>Accepts a well-formed email address</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.395Z</t>
+    <t>2026-06-18T14:25:36.721Z</t>
   </si>
   <si>
     <t>TC-ADV-02</t>
@@ -1220,6 +1189,9 @@
     <t>Accepts email with subdomain</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.722Z</t>
+  </si>
+  <si>
     <t>TC-ADV-03</t>
   </si>
   <si>
@@ -1238,9 +1210,6 @@
     <t>Rejects null and undefined inputs</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.396Z</t>
-  </si>
-  <si>
     <t>TC-ADV-06</t>
   </si>
   <si>
@@ -1262,7 +1231,7 @@
     <t>Accepts strong password meeting all requirements</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.399Z</t>
+    <t>2026-06-18T14:25:36.726Z</t>
   </si>
   <si>
     <t>TC-ADV-09</t>
@@ -1271,16 +1240,13 @@
     <t>Rejects password shorter than 8 characters</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.400Z</t>
-  </si>
-  <si>
     <t>TC-ADV-10</t>
   </si>
   <si>
     <t>Rejects password missing uppercase letter</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.401Z</t>
+    <t>2026-06-18T14:25:36.727Z</t>
   </si>
   <si>
     <t>TC-ADV-11</t>
@@ -1301,9 +1267,6 @@
     <t>Returns multiple failure reasons when multiple rules fail</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.402Z</t>
-  </si>
-  <si>
     <t>TC-ADV-14</t>
   </si>
   <si>
@@ -1313,21 +1276,24 @@
     <t>Correctly calculates age for a past birth date</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.728Z</t>
+  </si>
+  <si>
     <t>TC-ADV-15</t>
   </si>
   <si>
     <t>Returns 0 for null dob</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.729Z</t>
+  </si>
+  <si>
     <t>TC-ADV-16</t>
   </si>
   <si>
     <t>Returns 0 for invalid date string</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.403Z</t>
-  </si>
-  <si>
     <t>TC-ADV-17</t>
   </si>
   <si>
@@ -1349,15 +1315,15 @@
     <t>Accepts standard normal blood pressure string</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.730Z</t>
+  </si>
+  <si>
     <t>TC-ADV-20</t>
   </si>
   <si>
     <t>Accepts high but within range blood pressure</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.404Z</t>
-  </si>
-  <si>
     <t>TC-ADV-21</t>
   </si>
   <si>
@@ -1379,9 +1345,6 @@
     <t>Rejects out-of-range systolic values</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.405Z</t>
-  </si>
-  <si>
     <t>TC-ADV-25</t>
   </si>
   <si>
@@ -1391,7 +1354,10 @@
     <t>Correctly parses valid blood pressure into systolic and diastolic</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.409Z</t>
+    <t>2 ms</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:36.732Z</t>
   </si>
   <si>
     <t>TC-ADV-26</t>
@@ -1400,9 +1366,6 @@
     <t>Returns null for invalid blood pressure string</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.410Z</t>
-  </si>
-  <si>
     <t>TC-ADV-27</t>
   </si>
   <si>
@@ -1415,6 +1378,9 @@
     <t>Correctly parses hypertensive crisis values</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.733Z</t>
+  </si>
+  <si>
     <t>TC-ADV-29</t>
   </si>
   <si>
@@ -1424,33 +1390,27 @@
     <t>Returns value unchanged when within bounds</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.411Z</t>
-  </si>
-  <si>
     <t>TC-ADV-30</t>
   </si>
   <si>
     <t>Returns min when value is below minimum</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.412Z</t>
-  </si>
-  <si>
     <t>TC-ADV-31</t>
   </si>
   <si>
     <t>Returns max when value exceeds maximum</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.413Z</t>
-  </si>
-  <si>
     <t>TC-ADV-32</t>
   </si>
   <si>
     <t>Returns min for null input value</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.734Z</t>
+  </si>
+  <si>
     <t>TC-ADV-33</t>
   </si>
   <si>
@@ -1466,9 +1426,6 @@
     <t>Returns value unchanged when already in 0-100 range</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.414Z</t>
-  </si>
-  <si>
     <t>TC-ADV-35</t>
   </si>
   <si>
@@ -1487,9 +1444,6 @@
     <t>Rounds decimal accuracy to nearest integer</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.415Z</t>
-  </si>
-  <si>
     <t>TC-ADV-38</t>
   </si>
   <si>
@@ -1499,6 +1453,9 @@
     <t>Calculates correct percentage for partial progress</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.735Z</t>
+  </si>
+  <si>
     <t>TC-ADV-39</t>
   </si>
   <si>
@@ -1517,6 +1474,9 @@
     <t>Caps at 100 when current exceeds total</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.737Z</t>
+  </si>
+  <si>
     <t>TC-ADV-42</t>
   </si>
   <si>
@@ -1532,7 +1492,7 @@
     <t>Returns Beginner for zero sessions</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.416Z</t>
+    <t>2026-06-18T14:25:36.738Z</t>
   </si>
   <si>
     <t>TC-ADV-44</t>
@@ -1574,7 +1534,7 @@
     <t>Formats small calorie count correctly</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.417Z</t>
+    <t>2026-06-18T14:25:36.739Z</t>
   </si>
   <si>
     <t>TC-ADV-50</t>
@@ -1616,9 +1576,6 @@
     <t>Accepts boundary minimum heart rate 30 bpm</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.418Z</t>
-  </si>
-  <si>
     <t>TC-ADV-56</t>
   </si>
   <si>
@@ -1631,6 +1588,9 @@
     <t>Rejects heart rate below 30 bpm</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.740Z</t>
+  </si>
+  <si>
     <t>TC-ADV-58</t>
   </si>
   <si>
@@ -1649,9 +1609,6 @@
     <t>Correctly calculates male BMR</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.419Z</t>
-  </si>
-  <si>
     <t>TC-ADV-61</t>
   </si>
   <si>
@@ -1664,6 +1621,9 @@
     <t>Returns 0 for invalid gender input</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.741Z</t>
+  </si>
+  <si>
     <t>TC-ADV-63</t>
   </si>
   <si>
@@ -1676,9 +1636,6 @@
     <t>Returns 0 for zero age</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.420Z</t>
-  </si>
-  <si>
     <t>TC-ADV-65</t>
   </si>
   <si>
@@ -1694,6 +1651,9 @@
     <t>Returns 7 for dates exactly one week apart</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.742Z</t>
+  </si>
+  <si>
     <t>TC-ADV-67</t>
   </si>
   <si>
@@ -1721,7 +1681,7 @@
     <t>Returns a non-empty string</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.421Z</t>
+    <t>2026-06-18T14:25:36.743Z</t>
   </si>
   <si>
     <t>TC-ADV-71</t>
@@ -1730,15 +1690,15 @@
     <t>Starts with session_ prefix</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.422Z</t>
-  </si>
-  <si>
     <t>TC-ADV-72</t>
   </si>
   <si>
     <t>Generates unique IDs across calls</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.744Z</t>
+  </si>
+  <si>
     <t>TC-ADV-73</t>
   </si>
   <si>
@@ -1748,9 +1708,6 @@
     <t>Returns true for healthy BMI range</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.423Z</t>
-  </si>
-  <si>
     <t>TC-ADV-74</t>
   </si>
   <si>
@@ -1763,9 +1720,6 @@
     <t>Returns false for obese individual</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.424Z</t>
-  </si>
-  <si>
     <t>TC-ADV-76</t>
   </si>
   <si>
@@ -1793,6 +1747,9 @@
     <t>Returns 0 for null input</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.745Z</t>
+  </si>
+  <si>
     <t>TC-ADV-80</t>
   </si>
   <si>
@@ -1808,9 +1765,6 @@
     <t>Correctly sums session durations into total minutes</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.425Z</t>
-  </si>
-  <si>
     <t>TC-ADV-82</t>
   </si>
   <si>
@@ -1820,9 +1774,6 @@
     <t>TC-ADV-83</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.426Z</t>
-  </si>
-  <si>
     <t>TC-ADV-84</t>
   </si>
   <si>
@@ -1835,6 +1786,9 @@
     <t>Rounds fractional minutes to nearest integer</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.746Z</t>
+  </si>
+  <si>
     <t>TC-ADV-86</t>
   </si>
   <si>
@@ -1844,9 +1798,6 @@
     <t>Returns the most recent date from an array</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.427Z</t>
-  </si>
-  <si>
     <t>TC-ADV-87</t>
   </si>
   <si>
@@ -1871,7 +1822,7 @@
     <t>Correctly converts 180 mg/dL to mmol/L</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.428Z</t>
+    <t>2026-06-18T14:25:36.747Z</t>
   </si>
   <si>
     <t>TC-ADV-91</t>
@@ -1904,15 +1855,15 @@
     <t>Classifies normal blood sugar correctly</t>
   </si>
   <si>
+    <t>2026-06-18T14:25:36.748Z</t>
+  </si>
+  <si>
     <t>TC-ADV-96</t>
   </si>
   <si>
     <t>Classifies pre-diabetic range correctly</t>
   </si>
   <si>
-    <t>2026-06-18T13:17:11.429Z</t>
-  </si>
-  <si>
     <t>TC-ADV-97</t>
   </si>
   <si>
@@ -1929,6 +1880,9 @@
   </si>
   <si>
     <t>Classifies boundary fasting normal value 99 mg/dL</t>
+  </si>
+  <si>
+    <t>2026-06-18T14:25:36.749Z</t>
   </si>
   <si>
     <t>TC-ADV-100</t>
@@ -1977,7 +1931,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2002,11 +1956,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEBEE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2044,7 +1993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2060,9 +2009,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2404,18 +2350,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="7" width="40" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
     <col min="12" max="12" width="28" customWidth="1"/>
   </cols>
@@ -2446,13 +2392,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="4">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2460,7 +2406,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>5</v>
@@ -2913,7 +2859,7 @@
         <v>25</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>27</v>
@@ -2922,21 +2868,21 @@
         <v>27</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>75</v>
@@ -2951,7 +2897,7 @@
         <v>25</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>27</v>
@@ -2960,21 +2906,21 @@
         <v>27</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>75</v>
@@ -2989,7 +2935,7 @@
         <v>25</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>27</v>
@@ -2998,21 +2944,21 @@
         <v>27</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>75</v>
@@ -3027,7 +2973,7 @@
         <v>25</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>27</v>
@@ -3036,21 +2982,21 @@
         <v>27</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>75</v>
@@ -3065,7 +3011,7 @@
         <v>25</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>27</v>
@@ -3074,21 +3020,21 @@
         <v>27</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>75</v>
@@ -3103,7 +3049,7 @@
         <v>25</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J23" s="7" t="s">
         <v>27</v>
@@ -3112,21 +3058,21 @@
         <v>27</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>75</v>
@@ -3141,7 +3087,7 @@
         <v>25</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>27</v>
@@ -3150,21 +3096,21 @@
         <v>27</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>75</v>
@@ -3179,7 +3125,7 @@
         <v>25</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>27</v>
@@ -3188,39 +3134,39 @@
         <v>27</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>27</v>
@@ -3234,31 +3180,31 @@
         <v>117</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>118</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>119</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>27</v>
@@ -3272,31 +3218,31 @@
         <v>121</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>122</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>123</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>27</v>
@@ -3310,31 +3256,31 @@
         <v>125</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>126</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>127</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>27</v>
@@ -3348,358 +3294,358 @@
         <v>129</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K31" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K32" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K34" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="D35" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>119</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L36" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>23</v>
@@ -3711,7 +3657,7 @@
         <v>25</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J39" s="7" t="s">
         <v>27</v>
@@ -3720,24 +3666,24 @@
         <v>27</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>23</v>
@@ -3749,7 +3695,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>27</v>
@@ -3758,24 +3704,24 @@
         <v>27</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>23</v>
@@ -3787,7 +3733,7 @@
         <v>25</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J41" s="7" t="s">
         <v>27</v>
@@ -3796,24 +3742,24 @@
         <v>27</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>23</v>
@@ -3825,7 +3771,7 @@
         <v>25</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J42" s="7" t="s">
         <v>27</v>
@@ -3834,24 +3780,24 @@
         <v>27</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>23</v>
@@ -3863,7 +3809,7 @@
         <v>25</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>27</v>
@@ -3872,24 +3818,24 @@
         <v>27</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>23</v>
@@ -3901,7 +3847,7 @@
         <v>25</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J44" s="7" t="s">
         <v>27</v>
@@ -3910,24 +3856,24 @@
         <v>27</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>23</v>
@@ -3939,7 +3885,7 @@
         <v>25</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>27</v>
@@ -3948,24 +3894,24 @@
         <v>27</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>23</v>
@@ -3977,7 +3923,7 @@
         <v>25</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>27</v>
@@ -3986,62 +3932,62 @@
         <v>27</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>113</v>
+        <v>24</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>201</v>
+        <v>27</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>27</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>205</v>
+        <v>113</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>206</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>23</v>
@@ -4053,121 +3999,121 @@
         <v>25</v>
       </c>
       <c r="I48" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L48" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K48" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L48" s="7" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C49" s="7" t="s">
+      <c r="E49" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="J49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L49" s="7" t="s">
         <v>211</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D50" s="7" t="s">
+      <c r="E50" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L50" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I50" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="J50" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L50" s="7" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D51" s="7" t="s">
+      <c r="E51" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>212</v>
       </c>
       <c r="J51" s="7" t="s">
         <v>27</v>
@@ -4184,28 +4130,28 @@
         <v>221</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C52" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="E52" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" s="7" t="s">
         <v>223</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>212</v>
       </c>
       <c r="J52" s="7" t="s">
         <v>27</v>
@@ -4222,7 +4168,7 @@
         <v>225</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>226</v>
@@ -4231,7 +4177,7 @@
         <v>227</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>23</v>
@@ -4260,16 +4206,16 @@
         <v>230</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>180</v>
+        <v>231</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>23</v>
@@ -4281,7 +4227,7 @@
         <v>25</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J54" s="7" t="s">
         <v>27</v>
@@ -4290,24 +4236,24 @@
         <v>27</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>23</v>
@@ -4319,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J55" s="7" t="s">
         <v>27</v>
@@ -4328,24 +4274,24 @@
         <v>27</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D56" s="7" t="s">
         <v>241</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>23</v>
@@ -4374,104 +4320,104 @@
         <v>244</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C57" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="E57" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L57" s="7" t="s">
         <v>246</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K57" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L57" s="7" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B58" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D58" s="7" t="s">
+      <c r="J58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="J58" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K58" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L58" s="7" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B59" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D59" s="7" t="s">
+      <c r="E59" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>212</v>
       </c>
       <c r="J59" s="7" t="s">
         <v>27</v>
@@ -4488,16 +4434,16 @@
         <v>256</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>257</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>23</v>
@@ -4509,24 +4455,24 @@
         <v>25</v>
       </c>
       <c r="I60" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L60" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L60" s="7" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B61" s="7" t="s">
         <v>260</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>204</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>261</v>
@@ -4535,7 +4481,7 @@
         <v>262</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>23</v>
@@ -4547,7 +4493,7 @@
         <v>25</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>207</v>
+        <v>263</v>
       </c>
       <c r="J61" s="7" t="s">
         <v>27</v>
@@ -4556,24 +4502,24 @@
         <v>27</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>23</v>
@@ -4585,7 +4531,7 @@
         <v>25</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>207</v>
+        <v>268</v>
       </c>
       <c r="J62" s="7" t="s">
         <v>27</v>
@@ -4594,24 +4540,24 @@
         <v>27</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>23</v>
@@ -4623,7 +4569,7 @@
         <v>25</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J63" s="7" t="s">
         <v>27</v>
@@ -4632,37 +4578,37 @@
         <v>27</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B64" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I64" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C64" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I64" s="7" t="s">
-        <v>276</v>
-      </c>
       <c r="J64" s="7" t="s">
         <v>27</v>
       </c>
@@ -4670,37 +4616,37 @@
         <v>27</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B65" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C65" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I65" s="7" t="s">
-        <v>228</v>
-      </c>
       <c r="J65" s="7" t="s">
         <v>27</v>
       </c>
@@ -4708,37 +4654,37 @@
         <v>27</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I66" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>285</v>
-      </c>
       <c r="J66" s="7" t="s">
         <v>27</v>
       </c>
@@ -4746,62 +4692,62 @@
         <v>27</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>289</v>
       </c>
       <c r="E67" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I67" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="F67" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I67" s="7" t="s">
+      <c r="J67" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K67" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L67" s="7" t="s">
         <v>290</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K67" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L67" s="7" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="B68" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>295</v>
-      </c>
       <c r="E68" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>23</v>
@@ -4813,33 +4759,33 @@
         <v>25</v>
       </c>
       <c r="I68" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L68" s="7" t="s">
         <v>290</v>
-      </c>
-      <c r="J68" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K68" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L68" s="7" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>23</v>
@@ -4851,7 +4797,7 @@
         <v>25</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J69" s="7" t="s">
         <v>27</v>
@@ -4860,24 +4806,24 @@
         <v>27</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>23</v>
@@ -4889,7 +4835,7 @@
         <v>25</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J70" s="7" t="s">
         <v>27</v>
@@ -4898,24 +4844,24 @@
         <v>27</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>23</v>
@@ -4927,7 +4873,7 @@
         <v>25</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J71" s="7" t="s">
         <v>27</v>
@@ -4936,24 +4882,24 @@
         <v>27</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>23</v>
@@ -4965,7 +4911,7 @@
         <v>25</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J72" s="7" t="s">
         <v>27</v>
@@ -4974,24 +4920,24 @@
         <v>27</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>23</v>
@@ -5003,7 +4949,7 @@
         <v>25</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J73" s="7" t="s">
         <v>27</v>
@@ -5012,24 +4958,24 @@
         <v>27</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>23</v>
@@ -5041,7 +4987,7 @@
         <v>25</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J74" s="7" t="s">
         <v>27</v>
@@ -5050,24 +4996,24 @@
         <v>27</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>23</v>
@@ -5079,7 +5025,7 @@
         <v>25</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J75" s="7" t="s">
         <v>27</v>
@@ -5088,24 +5034,24 @@
         <v>27</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>23</v>
@@ -5117,7 +5063,7 @@
         <v>25</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J76" s="7" t="s">
         <v>27</v>
@@ -5126,24 +5072,24 @@
         <v>27</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>23</v>
@@ -5155,7 +5101,7 @@
         <v>25</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J77" s="7" t="s">
         <v>27</v>
@@ -5164,24 +5110,24 @@
         <v>27</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F78" s="7" t="s">
         <v>23</v>
@@ -5193,7 +5139,7 @@
         <v>25</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J78" s="7" t="s">
         <v>27</v>
@@ -5202,62 +5148,62 @@
         <v>27</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L79" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K79" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L79" s="7" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D80" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B80" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>324</v>
-      </c>
       <c r="E80" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>23</v>
@@ -5269,7 +5215,7 @@
         <v>25</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J80" s="7" t="s">
         <v>27</v>
@@ -5278,24 +5224,24 @@
         <v>27</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>23</v>
@@ -5307,7 +5253,7 @@
         <v>25</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J81" s="7" t="s">
         <v>27</v>
@@ -5316,24 +5262,24 @@
         <v>27</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>23</v>
@@ -5345,7 +5291,7 @@
         <v>25</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J82" s="7" t="s">
         <v>27</v>
@@ -5354,24 +5300,24 @@
         <v>27</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>23</v>
@@ -5383,7 +5329,7 @@
         <v>25</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J83" s="7" t="s">
         <v>27</v>
@@ -5397,19 +5343,19 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>23</v>
@@ -5421,7 +5367,7 @@
         <v>25</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J84" s="7" t="s">
         <v>27</v>
@@ -5435,19 +5381,19 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D85" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>335</v>
-      </c>
       <c r="E85" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>23</v>
@@ -5459,7 +5405,7 @@
         <v>25</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J85" s="7" t="s">
         <v>27</v>
@@ -5468,24 +5414,24 @@
         <v>27</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>23</v>
@@ -5497,7 +5443,7 @@
         <v>25</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J86" s="7" t="s">
         <v>27</v>
@@ -5506,62 +5452,62 @@
         <v>27</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K87" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L87" s="7" t="s">
         <v>339</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H87" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K87" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L87" s="7" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>23</v>
@@ -5573,7 +5519,7 @@
         <v>25</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J88" s="7" t="s">
         <v>27</v>
@@ -5582,24 +5528,24 @@
         <v>27</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>23</v>
@@ -5611,7 +5557,7 @@
         <v>25</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J89" s="7" t="s">
         <v>27</v>
@@ -5620,24 +5566,24 @@
         <v>27</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>23</v>
@@ -5649,7 +5595,7 @@
         <v>25</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J90" s="7" t="s">
         <v>27</v>
@@ -5658,24 +5604,24 @@
         <v>27</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>23</v>
@@ -5687,7 +5633,7 @@
         <v>25</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J91" s="7" t="s">
         <v>27</v>
@@ -5696,24 +5642,24 @@
         <v>27</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>23</v>
@@ -5725,7 +5671,7 @@
         <v>25</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J92" s="7" t="s">
         <v>27</v>
@@ -5734,24 +5680,24 @@
         <v>27</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>23</v>
@@ -5763,7 +5709,7 @@
         <v>25</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J93" s="7" t="s">
         <v>27</v>
@@ -5772,24 +5718,24 @@
         <v>27</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>23</v>
@@ -5801,7 +5747,7 @@
         <v>25</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J94" s="7" t="s">
         <v>27</v>
@@ -5810,24 +5756,24 @@
         <v>27</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>23</v>
@@ -5839,7 +5785,7 @@
         <v>25</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J95" s="7" t="s">
         <v>27</v>
@@ -5848,138 +5794,138 @@
         <v>27</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C96" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I96" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K96" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L96" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G96" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H96" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I96" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J96" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K96" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L96" s="7" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C97" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I97" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K97" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L97" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H97" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L97" s="7" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C98" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L98" s="7" t="s">
         <v>360</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H98" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I98" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J98" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L98" s="7" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>23</v>
@@ -5991,7 +5937,7 @@
         <v>25</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J99" s="7" t="s">
         <v>27</v>
@@ -6000,24 +5946,24 @@
         <v>27</v>
       </c>
       <c r="L99" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C100" s="7" t="s">
         <v>370</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>23</v>
@@ -6029,7 +5975,7 @@
         <v>25</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J100" s="7" t="s">
         <v>27</v>
@@ -6038,24 +5984,24 @@
         <v>27</v>
       </c>
       <c r="L100" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C101" s="7" t="s">
         <v>370</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>23</v>
@@ -6067,7 +6013,7 @@
         <v>25</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J101" s="7" t="s">
         <v>27</v>
@@ -6081,57 +6027,57 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I102" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K102" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L102" s="7" t="s">
         <v>377</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H102" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I102" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J102" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K102" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L102" s="7" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>23</v>
@@ -6143,7 +6089,7 @@
         <v>25</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J103" s="7" t="s">
         <v>27</v>
@@ -6152,24 +6098,24 @@
         <v>27</v>
       </c>
       <c r="L103" s="7" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>23</v>
@@ -6181,7 +6127,7 @@
         <v>25</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="J104" s="7" t="s">
         <v>27</v>
@@ -6190,24 +6136,24 @@
         <v>27</v>
       </c>
       <c r="L104" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>23</v>
@@ -6219,7 +6165,7 @@
         <v>25</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J105" s="7" t="s">
         <v>27</v>
@@ -6228,24 +6174,24 @@
         <v>27</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C106" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D106" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="D106" s="7" t="s">
-        <v>392</v>
-      </c>
       <c r="E106" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>23</v>
@@ -6257,7 +6203,7 @@
         <v>25</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J106" s="7" t="s">
         <v>27</v>
@@ -6266,24 +6212,24 @@
         <v>27</v>
       </c>
       <c r="L106" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>23</v>
@@ -6295,7 +6241,7 @@
         <v>25</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J107" s="7" t="s">
         <v>27</v>
@@ -6304,24 +6250,24 @@
         <v>27</v>
       </c>
       <c r="L107" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>23</v>
@@ -6333,7 +6279,7 @@
         <v>25</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J108" s="7" t="s">
         <v>27</v>
@@ -6342,24 +6288,24 @@
         <v>27</v>
       </c>
       <c r="L108" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C109" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D109" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D109" s="7" t="s">
-        <v>400</v>
-      </c>
       <c r="E109" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>23</v>
@@ -6371,7 +6317,7 @@
         <v>25</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J109" s="7" t="s">
         <v>27</v>
@@ -6380,24 +6326,24 @@
         <v>27</v>
       </c>
       <c r="L109" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>23</v>
@@ -6409,7 +6355,7 @@
         <v>25</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J110" s="7" t="s">
         <v>27</v>
@@ -6418,24 +6364,24 @@
         <v>27</v>
       </c>
       <c r="L110" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>23</v>
@@ -6447,7 +6393,7 @@
         <v>25</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J111" s="7" t="s">
         <v>27</v>
@@ -6456,24 +6402,24 @@
         <v>27</v>
       </c>
       <c r="L111" s="7" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>23</v>
@@ -6485,7 +6431,7 @@
         <v>25</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J112" s="7" t="s">
         <v>27</v>
@@ -6494,24 +6440,24 @@
         <v>27</v>
       </c>
       <c r="L112" s="7" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>23</v>
@@ -6523,7 +6469,7 @@
         <v>25</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>285</v>
+        <v>203</v>
       </c>
       <c r="J113" s="7" t="s">
         <v>27</v>
@@ -6532,24 +6478,24 @@
         <v>27</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>23</v>
@@ -6561,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J114" s="7" t="s">
         <v>27</v>
@@ -6570,24 +6516,24 @@
         <v>27</v>
       </c>
       <c r="L114" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>23</v>
@@ -6599,7 +6545,7 @@
         <v>25</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="J115" s="7" t="s">
         <v>27</v>
@@ -6608,24 +6554,24 @@
         <v>27</v>
       </c>
       <c r="L115" s="7" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="7" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C116" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D116" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>417</v>
-      </c>
       <c r="E116" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>23</v>
@@ -6637,7 +6583,7 @@
         <v>25</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J116" s="7" t="s">
         <v>27</v>
@@ -6646,24 +6592,24 @@
         <v>27</v>
       </c>
       <c r="L116" s="7" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>23</v>
@@ -6675,7 +6621,7 @@
         <v>25</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J117" s="7" t="s">
         <v>27</v>
@@ -6684,24 +6630,24 @@
         <v>27</v>
       </c>
       <c r="L117" s="7" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>23</v>
@@ -6713,7 +6659,7 @@
         <v>25</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J118" s="7" t="s">
         <v>27</v>
@@ -6722,24 +6668,24 @@
         <v>27</v>
       </c>
       <c r="L118" s="7" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>23</v>
@@ -6751,7 +6697,7 @@
         <v>25</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J119" s="7" t="s">
         <v>27</v>
@@ -6765,19 +6711,19 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>23</v>
@@ -6789,7 +6735,7 @@
         <v>25</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J120" s="7" t="s">
         <v>27</v>
@@ -6798,24 +6744,24 @@
         <v>27</v>
       </c>
       <c r="L120" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>23</v>
@@ -6827,7 +6773,7 @@
         <v>25</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J121" s="7" t="s">
         <v>27</v>
@@ -6836,24 +6782,24 @@
         <v>27</v>
       </c>
       <c r="L121" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>23</v>
@@ -6865,7 +6811,7 @@
         <v>25</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J122" s="7" t="s">
         <v>27</v>
@@ -6874,24 +6820,24 @@
         <v>27</v>
       </c>
       <c r="L122" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C123" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D123" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="D123" s="7" t="s">
-        <v>435</v>
-      </c>
       <c r="E123" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>23</v>
@@ -6903,7 +6849,7 @@
         <v>25</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J123" s="7" t="s">
         <v>27</v>
@@ -6912,24 +6858,24 @@
         <v>27</v>
       </c>
       <c r="L123" s="7" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="7" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>23</v>
@@ -6941,7 +6887,7 @@
         <v>25</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J124" s="7" t="s">
         <v>27</v>
@@ -6950,24 +6896,24 @@
         <v>27</v>
       </c>
       <c r="L124" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>23</v>
@@ -6979,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J125" s="7" t="s">
         <v>27</v>
@@ -6988,24 +6934,24 @@
         <v>27</v>
       </c>
       <c r="L125" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="7" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>23</v>
@@ -7017,7 +6963,7 @@
         <v>25</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J126" s="7" t="s">
         <v>27</v>
@@ -7026,24 +6972,24 @@
         <v>27</v>
       </c>
       <c r="L126" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>23</v>
@@ -7055,7 +7001,7 @@
         <v>25</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J127" s="7" t="s">
         <v>27</v>
@@ -7064,24 +7010,24 @@
         <v>27</v>
       </c>
       <c r="L127" s="7" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="7" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>448</v>
+        <v>398</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>23</v>
@@ -7093,7 +7039,7 @@
         <v>25</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J128" s="7" t="s">
         <v>27</v>
@@ -7102,24 +7048,24 @@
         <v>27</v>
       </c>
       <c r="L128" s="7" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F129" s="7" t="s">
         <v>23</v>
@@ -7131,7 +7077,7 @@
         <v>25</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J129" s="7" t="s">
         <v>27</v>
@@ -7140,24 +7086,24 @@
         <v>27</v>
       </c>
       <c r="L129" s="7" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="7" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>406</v>
+        <v>446</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F130" s="7" t="s">
         <v>23</v>
@@ -7169,7 +7115,7 @@
         <v>25</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>285</v>
+        <v>447</v>
       </c>
       <c r="J130" s="7" t="s">
         <v>27</v>
@@ -7178,24 +7124,24 @@
         <v>27</v>
       </c>
       <c r="L130" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F131" s="7" t="s">
         <v>23</v>
@@ -7207,7 +7153,7 @@
         <v>25</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J131" s="7" t="s">
         <v>27</v>
@@ -7216,24 +7162,24 @@
         <v>27</v>
       </c>
       <c r="L131" s="7" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F132" s="7" t="s">
         <v>23</v>
@@ -7245,7 +7191,7 @@
         <v>25</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J132" s="7" t="s">
         <v>27</v>
@@ -7254,24 +7200,24 @@
         <v>27</v>
       </c>
       <c r="L132" s="7" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>23</v>
@@ -7283,7 +7229,7 @@
         <v>25</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J133" s="7" t="s">
         <v>27</v>
@@ -7292,24 +7238,24 @@
         <v>27</v>
       </c>
       <c r="L133" s="7" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="7" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D134" s="7" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F134" s="7" t="s">
         <v>23</v>
@@ -7321,7 +7267,7 @@
         <v>25</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J134" s="7" t="s">
         <v>27</v>
@@ -7330,24 +7276,24 @@
         <v>27</v>
       </c>
       <c r="L134" s="7" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F135" s="7" t="s">
         <v>23</v>
@@ -7359,7 +7305,7 @@
         <v>25</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J135" s="7" t="s">
         <v>27</v>
@@ -7368,24 +7314,24 @@
         <v>27</v>
       </c>
       <c r="L135" s="7" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="7" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>23</v>
@@ -7397,7 +7343,7 @@
         <v>25</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J136" s="7" t="s">
         <v>27</v>
@@ -7406,24 +7352,24 @@
         <v>27</v>
       </c>
       <c r="L136" s="7" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F137" s="7" t="s">
         <v>23</v>
@@ -7435,7 +7381,7 @@
         <v>25</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J137" s="7" t="s">
         <v>27</v>
@@ -7444,24 +7390,24 @@
         <v>27</v>
       </c>
       <c r="L137" s="7" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="7" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C138" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="D138" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="D138" s="7" t="s">
-        <v>474</v>
-      </c>
       <c r="E138" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F138" s="7" t="s">
         <v>23</v>
@@ -7473,7 +7419,7 @@
         <v>25</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J138" s="7" t="s">
         <v>27</v>
@@ -7482,24 +7428,24 @@
         <v>27</v>
       </c>
       <c r="L138" s="7" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F139" s="7" t="s">
         <v>23</v>
@@ -7511,7 +7457,7 @@
         <v>25</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J139" s="7" t="s">
         <v>27</v>
@@ -7520,24 +7466,24 @@
         <v>27</v>
       </c>
       <c r="L139" s="7" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="7" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F140" s="7" t="s">
         <v>23</v>
@@ -7549,7 +7495,7 @@
         <v>25</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J140" s="7" t="s">
         <v>27</v>
@@ -7558,24 +7504,24 @@
         <v>27</v>
       </c>
       <c r="L140" s="7" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F141" s="7" t="s">
         <v>23</v>
@@ -7587,7 +7533,7 @@
         <v>25</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J141" s="7" t="s">
         <v>27</v>
@@ -7596,24 +7542,24 @@
         <v>27</v>
       </c>
       <c r="L141" s="7" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="7" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F142" s="7" t="s">
         <v>23</v>
@@ -7625,7 +7571,7 @@
         <v>25</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J142" s="7" t="s">
         <v>27</v>
@@ -7634,24 +7580,24 @@
         <v>27</v>
       </c>
       <c r="L142" s="7" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D143" s="7" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F143" s="7" t="s">
         <v>23</v>
@@ -7663,7 +7609,7 @@
         <v>25</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J143" s="7" t="s">
         <v>27</v>
@@ -7672,24 +7618,24 @@
         <v>27</v>
       </c>
       <c r="L143" s="7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="7" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D144" s="7" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F144" s="7" t="s">
         <v>23</v>
@@ -7701,7 +7647,7 @@
         <v>25</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J144" s="7" t="s">
         <v>27</v>
@@ -7710,24 +7656,24 @@
         <v>27</v>
       </c>
       <c r="L144" s="7" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F145" s="7" t="s">
         <v>23</v>
@@ -7739,7 +7685,7 @@
         <v>25</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J145" s="7" t="s">
         <v>27</v>
@@ -7748,24 +7694,24 @@
         <v>27</v>
       </c>
       <c r="L145" s="7" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="7" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F146" s="7" t="s">
         <v>23</v>
@@ -7777,7 +7723,7 @@
         <v>25</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J146" s="7" t="s">
         <v>27</v>
@@ -7786,24 +7732,24 @@
         <v>27</v>
       </c>
       <c r="L146" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F147" s="7" t="s">
         <v>23</v>
@@ -7815,7 +7761,7 @@
         <v>25</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J147" s="7" t="s">
         <v>27</v>
@@ -7824,24 +7770,24 @@
         <v>27</v>
       </c>
       <c r="L147" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="7" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C148" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="D148" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="D148" s="7" t="s">
-        <v>499</v>
-      </c>
       <c r="E148" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F148" s="7" t="s">
         <v>23</v>
@@ -7853,7 +7799,7 @@
         <v>25</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J148" s="7" t="s">
         <v>27</v>
@@ -7862,24 +7808,24 @@
         <v>27</v>
       </c>
       <c r="L148" s="7" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D149" s="7" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F149" s="7" t="s">
         <v>23</v>
@@ -7891,7 +7837,7 @@
         <v>25</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J149" s="7" t="s">
         <v>27</v>
@@ -7900,24 +7846,24 @@
         <v>27</v>
       </c>
       <c r="L149" s="7" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="7" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="D150" s="7" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F150" s="7" t="s">
         <v>23</v>
@@ -7929,7 +7875,7 @@
         <v>25</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J150" s="7" t="s">
         <v>27</v>
@@ -7938,24 +7884,24 @@
         <v>27</v>
       </c>
       <c r="L150" s="7" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F151" s="7" t="s">
         <v>23</v>
@@ -7967,7 +7913,7 @@
         <v>25</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J151" s="7" t="s">
         <v>27</v>
@@ -7976,24 +7922,24 @@
         <v>27</v>
       </c>
       <c r="L151" s="7" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="7" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="D152" s="7" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F152" s="7" t="s">
         <v>23</v>
@@ -8005,7 +7951,7 @@
         <v>25</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J152" s="7" t="s">
         <v>27</v>
@@ -8014,24 +7960,24 @@
         <v>27</v>
       </c>
       <c r="L152" s="7" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C153" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="D153" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="D153" s="7" t="s">
-        <v>511</v>
-      </c>
       <c r="E153" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F153" s="7" t="s">
         <v>23</v>
@@ -8043,7 +7989,7 @@
         <v>25</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J153" s="7" t="s">
         <v>27</v>
@@ -8052,24 +7998,24 @@
         <v>27</v>
       </c>
       <c r="L153" s="7" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="7" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F154" s="7" t="s">
         <v>23</v>
@@ -8081,7 +8027,7 @@
         <v>25</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J154" s="7" t="s">
         <v>27</v>
@@ -8090,24 +8036,24 @@
         <v>27</v>
       </c>
       <c r="L154" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F155" s="7" t="s">
         <v>23</v>
@@ -8119,7 +8065,7 @@
         <v>25</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J155" s="7" t="s">
         <v>27</v>
@@ -8128,24 +8074,24 @@
         <v>27</v>
       </c>
       <c r="L155" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="7" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F156" s="7" t="s">
         <v>23</v>
@@ -8157,7 +8103,7 @@
         <v>25</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J156" s="7" t="s">
         <v>27</v>
@@ -8166,24 +8112,24 @@
         <v>27</v>
       </c>
       <c r="L156" s="7" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F157" s="7" t="s">
         <v>23</v>
@@ -8195,7 +8141,7 @@
         <v>25</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J157" s="7" t="s">
         <v>27</v>
@@ -8204,24 +8150,24 @@
         <v>27</v>
       </c>
       <c r="L157" s="7" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="7" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F158" s="7" t="s">
         <v>23</v>
@@ -8233,7 +8179,7 @@
         <v>25</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J158" s="7" t="s">
         <v>27</v>
@@ -8242,24 +8188,24 @@
         <v>27</v>
       </c>
       <c r="L158" s="7" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C159" s="7" t="s">
         <v>517</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F159" s="7" t="s">
         <v>23</v>
@@ -8271,7 +8217,7 @@
         <v>25</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J159" s="7" t="s">
         <v>27</v>
@@ -8280,24 +8226,24 @@
         <v>27</v>
       </c>
       <c r="L159" s="7" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="7" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C160" s="7" t="s">
         <v>517</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F160" s="7" t="s">
         <v>23</v>
@@ -8309,7 +8255,7 @@
         <v>25</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J160" s="7" t="s">
         <v>27</v>
@@ -8318,24 +8264,24 @@
         <v>27</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F161" s="7" t="s">
         <v>23</v>
@@ -8347,7 +8293,7 @@
         <v>25</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J161" s="7" t="s">
         <v>27</v>
@@ -8356,24 +8302,24 @@
         <v>27</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="7" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F162" s="7" t="s">
         <v>23</v>
@@ -8385,7 +8331,7 @@
         <v>25</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J162" s="7" t="s">
         <v>27</v>
@@ -8394,24 +8340,24 @@
         <v>27</v>
       </c>
       <c r="L162" s="7" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F163" s="7" t="s">
         <v>23</v>
@@ -8423,7 +8369,7 @@
         <v>25</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>27</v>
@@ -8432,24 +8378,24 @@
         <v>27</v>
       </c>
       <c r="L163" s="7" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="7" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>537</v>
+        <v>398</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F164" s="7" t="s">
         <v>23</v>
@@ -8461,7 +8407,7 @@
         <v>25</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>27</v>
@@ -8470,24 +8416,24 @@
         <v>27</v>
       </c>
       <c r="L164" s="7" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F165" s="7" t="s">
         <v>23</v>
@@ -8499,7 +8445,7 @@
         <v>25</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J165" s="7" t="s">
         <v>27</v>
@@ -8508,24 +8454,24 @@
         <v>27</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="7" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>406</v>
+        <v>533</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F166" s="7" t="s">
         <v>23</v>
@@ -8537,7 +8483,7 @@
         <v>25</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J166" s="7" t="s">
         <v>27</v>
@@ -8546,24 +8492,24 @@
         <v>27</v>
       </c>
       <c r="L166" s="7" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F167" s="7" t="s">
         <v>23</v>
@@ -8575,7 +8521,7 @@
         <v>25</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>27</v>
@@ -8584,24 +8530,24 @@
         <v>27</v>
       </c>
       <c r="L167" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="7" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F168" s="7" t="s">
         <v>23</v>
@@ -8613,7 +8559,7 @@
         <v>25</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J168" s="7" t="s">
         <v>27</v>
@@ -8622,24 +8568,24 @@
         <v>27</v>
       </c>
       <c r="L168" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F169" s="7" t="s">
         <v>23</v>
@@ -8651,7 +8597,7 @@
         <v>25</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J169" s="7" t="s">
         <v>27</v>
@@ -8660,24 +8606,24 @@
         <v>27</v>
       </c>
       <c r="L169" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="7" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C170" s="7" t="s">
         <v>542</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F170" s="7" t="s">
         <v>23</v>
@@ -8689,7 +8635,7 @@
         <v>25</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J170" s="7" t="s">
         <v>27</v>
@@ -8698,24 +8644,24 @@
         <v>27</v>
       </c>
       <c r="L170" s="7" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>542</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F171" s="7" t="s">
         <v>23</v>
@@ -8727,7 +8673,7 @@
         <v>25</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>27</v>
@@ -8736,24 +8682,24 @@
         <v>27</v>
       </c>
       <c r="L171" s="7" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F172" s="7" t="s">
         <v>23</v>
@@ -8765,7 +8711,7 @@
         <v>25</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J172" s="7" t="s">
         <v>27</v>
@@ -8774,24 +8720,24 @@
         <v>27</v>
       </c>
       <c r="L172" s="7" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D173" s="7" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F173" s="7" t="s">
         <v>23</v>
@@ -8803,7 +8749,7 @@
         <v>25</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J173" s="7" t="s">
         <v>27</v>
@@ -8812,24 +8758,24 @@
         <v>27</v>
       </c>
       <c r="L173" s="7" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="D174" s="7" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F174" s="7" t="s">
         <v>23</v>
@@ -8841,7 +8787,7 @@
         <v>25</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J174" s="7" t="s">
         <v>27</v>
@@ -8850,24 +8796,24 @@
         <v>27</v>
       </c>
       <c r="L174" s="7" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C175" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="D175" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="D175" s="7" t="s">
-        <v>562</v>
-      </c>
       <c r="E175" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F175" s="7" t="s">
         <v>23</v>
@@ -8879,7 +8825,7 @@
         <v>25</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J175" s="7" t="s">
         <v>27</v>
@@ -8888,24 +8834,24 @@
         <v>27</v>
       </c>
       <c r="L175" s="7" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F176" s="7" t="s">
         <v>23</v>
@@ -8917,7 +8863,7 @@
         <v>25</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J176" s="7" t="s">
         <v>27</v>
@@ -8926,24 +8872,24 @@
         <v>27</v>
       </c>
       <c r="L176" s="7" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="D177" s="7" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F177" s="7" t="s">
         <v>23</v>
@@ -8955,7 +8901,7 @@
         <v>25</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J177" s="7" t="s">
         <v>27</v>
@@ -8964,24 +8910,24 @@
         <v>27</v>
       </c>
       <c r="L177" s="7" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F178" s="7" t="s">
         <v>23</v>
@@ -8993,7 +8939,7 @@
         <v>25</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J178" s="7" t="s">
         <v>27</v>
@@ -9002,24 +8948,24 @@
         <v>27</v>
       </c>
       <c r="L178" s="7" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C179" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="D179" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D179" s="7" t="s">
-        <v>573</v>
-      </c>
       <c r="E179" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F179" s="7" t="s">
         <v>23</v>
@@ -9031,7 +8977,7 @@
         <v>25</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J179" s="7" t="s">
         <v>27</v>
@@ -9040,24 +8986,24 @@
         <v>27</v>
       </c>
       <c r="L179" s="7" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="7" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F180" s="7" t="s">
         <v>23</v>
@@ -9069,7 +9015,7 @@
         <v>25</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J180" s="7" t="s">
         <v>27</v>
@@ -9078,24 +9024,24 @@
         <v>27</v>
       </c>
       <c r="L180" s="7" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F181" s="7" t="s">
         <v>23</v>
@@ -9107,7 +9053,7 @@
         <v>25</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J181" s="7" t="s">
         <v>27</v>
@@ -9116,24 +9062,24 @@
         <v>27</v>
       </c>
       <c r="L181" s="7" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F182" s="7" t="s">
         <v>23</v>
@@ -9145,7 +9091,7 @@
         <v>25</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J182" s="7" t="s">
         <v>27</v>
@@ -9154,24 +9100,24 @@
         <v>27</v>
       </c>
       <c r="L182" s="7" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F183" s="7" t="s">
         <v>23</v>
@@ -9183,7 +9129,7 @@
         <v>25</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J183" s="7" t="s">
         <v>27</v>
@@ -9192,24 +9138,24 @@
         <v>27</v>
       </c>
       <c r="L183" s="7" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="7" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F184" s="7" t="s">
         <v>23</v>
@@ -9221,7 +9167,7 @@
         <v>25</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J184" s="7" t="s">
         <v>27</v>
@@ -9230,24 +9176,24 @@
         <v>27</v>
       </c>
       <c r="L184" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F185" s="7" t="s">
         <v>23</v>
@@ -9259,7 +9205,7 @@
         <v>25</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J185" s="7" t="s">
         <v>27</v>
@@ -9268,24 +9214,24 @@
         <v>27</v>
       </c>
       <c r="L185" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="7" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D186" s="7" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F186" s="7" t="s">
         <v>23</v>
@@ -9297,7 +9243,7 @@
         <v>25</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J186" s="7" t="s">
         <v>27</v>
@@ -9306,24 +9252,24 @@
         <v>27</v>
       </c>
       <c r="L186" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D187" s="7" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F187" s="7" t="s">
         <v>23</v>
@@ -9335,7 +9281,7 @@
         <v>25</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J187" s="7" t="s">
         <v>27</v>
@@ -9344,24 +9290,24 @@
         <v>27</v>
       </c>
       <c r="L187" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="7" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F188" s="7" t="s">
         <v>23</v>
@@ -9373,7 +9319,7 @@
         <v>25</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J188" s="7" t="s">
         <v>27</v>
@@ -9382,24 +9328,24 @@
         <v>27</v>
       </c>
       <c r="L188" s="7" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="D189" s="7" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F189" s="7" t="s">
         <v>23</v>
@@ -9411,7 +9357,7 @@
         <v>25</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J189" s="7" t="s">
         <v>27</v>
@@ -9420,62 +9366,62 @@
         <v>27</v>
       </c>
       <c r="L189" s="7" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="7" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="D190" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G190" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H190" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="J190" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="K190" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L190" s="7" t="s">
         <v>591</v>
-      </c>
-      <c r="E190" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G190" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H190" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I190" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J190" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K190" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L190" s="7" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D191" s="7" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F191" s="7" t="s">
         <v>23</v>
@@ -9487,7 +9433,7 @@
         <v>25</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J191" s="7" t="s">
         <v>27</v>
@@ -9496,24 +9442,24 @@
         <v>27</v>
       </c>
       <c r="L191" s="7" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="7" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D192" s="7" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E192" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F192" s="7" t="s">
         <v>23</v>
@@ -9525,7 +9471,7 @@
         <v>25</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J192" s="7" t="s">
         <v>27</v>
@@ -9534,24 +9480,24 @@
         <v>27</v>
       </c>
       <c r="L192" s="7" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>608</v>
+        <v>452</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F193" s="7" t="s">
         <v>23</v>
@@ -9563,7 +9509,7 @@
         <v>25</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J193" s="7" t="s">
         <v>27</v>
@@ -9572,24 +9518,24 @@
         <v>27</v>
       </c>
       <c r="L193" s="7" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="7" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F194" s="7" t="s">
         <v>23</v>
@@ -9601,7 +9547,7 @@
         <v>25</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J194" s="7" t="s">
         <v>27</v>
@@ -9610,24 +9556,24 @@
         <v>27</v>
       </c>
       <c r="L194" s="7" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>463</v>
+        <v>602</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F195" s="7" t="s">
         <v>23</v>
@@ -9639,7 +9585,7 @@
         <v>25</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="J195" s="7" t="s">
         <v>27</v>
@@ -9648,24 +9594,24 @@
         <v>27</v>
       </c>
       <c r="L195" s="7" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="D196" s="7" t="s">
-        <v>614</v>
+        <v>577</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F196" s="7" t="s">
         <v>23</v>
@@ -9677,7 +9623,7 @@
         <v>25</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J196" s="7" t="s">
         <v>27</v>
@@ -9686,24 +9632,24 @@
         <v>27</v>
       </c>
       <c r="L196" s="7" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D197" s="7" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F197" s="7" t="s">
         <v>23</v>
@@ -9715,7 +9661,7 @@
         <v>25</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J197" s="7" t="s">
         <v>27</v>
@@ -9724,24 +9670,24 @@
         <v>27</v>
       </c>
       <c r="L197" s="7" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="7" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
       <c r="E198" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F198" s="7" t="s">
         <v>23</v>
@@ -9753,7 +9699,7 @@
         <v>25</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J198" s="7" t="s">
         <v>27</v>
@@ -9762,24 +9708,24 @@
         <v>27</v>
       </c>
       <c r="L198" s="7" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F199" s="7" t="s">
         <v>23</v>
@@ -9791,7 +9737,7 @@
         <v>25</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J199" s="7" t="s">
         <v>27</v>
@@ -9800,24 +9746,24 @@
         <v>27</v>
       </c>
       <c r="L199" s="7" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="E200" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F200" s="7" t="s">
         <v>23</v>
@@ -9829,7 +9775,7 @@
         <v>25</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J200" s="7" t="s">
         <v>27</v>
@@ -9838,24 +9784,24 @@
         <v>27</v>
       </c>
       <c r="L200" s="7" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F201" s="7" t="s">
         <v>23</v>
@@ -9867,7 +9813,7 @@
         <v>25</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J201" s="7" t="s">
         <v>27</v>
@@ -9876,24 +9822,24 @@
         <v>27</v>
       </c>
       <c r="L201" s="7" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="D202" s="7" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F202" s="7" t="s">
         <v>23</v>
@@ -9905,7 +9851,7 @@
         <v>25</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J202" s="7" t="s">
         <v>27</v>
@@ -9914,24 +9860,24 @@
         <v>27</v>
       </c>
       <c r="L202" s="7" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F203" s="7" t="s">
         <v>23</v>
@@ -9943,7 +9889,7 @@
         <v>25</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J203" s="7" t="s">
         <v>27</v>
@@ -9952,24 +9898,24 @@
         <v>27</v>
       </c>
       <c r="L203" s="7" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>23</v>
@@ -9981,7 +9927,7 @@
         <v>25</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>27</v>
@@ -9990,24 +9936,24 @@
         <v>27</v>
       </c>
       <c r="L204" s="7" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C205" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="D205" s="7" t="s">
         <v>625</v>
       </c>
-      <c r="D205" s="7" t="s">
-        <v>635</v>
-      </c>
       <c r="E205" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>23</v>
@@ -10019,7 +9965,7 @@
         <v>25</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="J205" s="7" t="s">
         <v>27</v>
@@ -10028,83 +9974,7 @@
         <v>27</v>
       </c>
       <c r="L205" s="7" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A206" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="B206" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C206" s="7" t="s">
-        <v>625</v>
-      </c>
-      <c r="D206" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="E206" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F206" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G206" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H206" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I206" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J206" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K206" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L206" s="7" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A207" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="B207" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>625</v>
-      </c>
-      <c r="D207" s="7" t="s">
-        <v>639</v>
-      </c>
-      <c r="E207" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F207" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G207" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H207" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I207" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="J207" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K207" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L207" s="7" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
